--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2462-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2462-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{117B7DC3-4EC4-48FF-8892-E38B509D1D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D40F593A-4711-4728-B226-D1B879CAF101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B40C76C6-71C4-4331-9CD0-300A760EB0B4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F9B49547-6D4B-4665-B95B-A92249B0457D}"/>
   </bookViews>
   <sheets>
     <sheet name="2462-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1502,27 +1502,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4ACC48-5113-4792-B2DB-8942FD287385}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E6ED7A-AE42-48CA-B95C-3E91A1D6FB90}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1555,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1592,7 +1591,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1644,7 +1643,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1712,7 +1711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1784,7 +1783,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -2000,7 +1999,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2144,7 +2143,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2216,7 +2215,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2288,7 +2287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2360,7 +2359,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2504,7 +2503,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2576,7 +2575,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2720,7 +2719,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2792,7 +2791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2864,7 +2863,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -3008,7 +3007,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3080,7 +3079,7 @@
         <v>7.64</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3152,7 +3151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3224,7 +3223,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3368,7 +3367,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3440,7 +3439,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3512,7 +3511,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3584,7 +3583,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3656,7 +3655,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3728,7 +3727,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3872,7 +3871,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3944,7 +3943,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -4016,7 +4015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4088,7 +4087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4160,7 +4159,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1990</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1989</v>
       </c>
@@ -4304,7 +4303,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34" t="s">
         <v>59</v>
       </c>
